--- a/data/vip2025.xlsx
+++ b/data/vip2025.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isabelhaas/Documents/Coding/aytogermany/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E068C319-0CE6-DD4F-81E0-7F8FF9A07FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EDA950C-A54E-A746-8BCB-FD998D3DC574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1300" windowWidth="20920" windowHeight="19440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nights" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="23">
   <si>
     <t>lights</t>
   </si>
@@ -53,6 +53,42 @@
   </si>
   <si>
     <t>Viki</t>
+  </si>
+  <si>
+    <t>Leandro</t>
+  </si>
+  <si>
+    <t>Calvin O.</t>
+  </si>
+  <si>
+    <t>Jonny</t>
+  </si>
+  <si>
+    <t>Sidar</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>Rob</t>
+  </si>
+  <si>
+    <t>Nico</t>
+  </si>
+  <si>
+    <t>Lennert</t>
+  </si>
+  <si>
+    <t>Xander</t>
+  </si>
+  <si>
+    <t>Calvin S.</t>
+  </si>
+  <si>
+    <t>Olli</t>
+  </si>
+  <si>
+    <t>Jimi</t>
   </si>
 </sst>
 </file>
@@ -74,12 +110,24 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -124,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -141,13 +189,8 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,7 +496,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" bestFit="1" customWidth="1"/>
@@ -461,7 +504,7 @@
     <col min="12" max="12" width="12.5" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
@@ -496,131 +539,180 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="6"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="8"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="6"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="8"/>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="8"/>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="8"/>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="8"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="8"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="8"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="8"/>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" s="5">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/vip2025.xlsx
+++ b/data/vip2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isabelhaas/Documents/Coding/aytogermany/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EDA950C-A54E-A746-8BCB-FD998D3DC574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE86BF9-2D52-BD49-BECB-2667BF3E9456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13220" yWindow="1120" windowWidth="20980" windowHeight="19440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nights" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="23">
   <si>
     <t>lights</t>
   </si>
@@ -496,7 +496,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" bestFit="1" customWidth="1"/>
@@ -540,7 +540,7 @@
       </c>
     </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
+      <c r="B2" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
@@ -564,7 +564,7 @@
       <c r="I2" t="s">
         <v>14</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="7" t="s">
         <v>15</v>
       </c>
       <c r="K2" t="s">
@@ -599,7 +599,7 @@
       <c r="I3" t="s">
         <v>16</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="7" t="s">
         <v>15</v>
       </c>
       <c r="K3" t="s">
@@ -631,10 +631,10 @@
       <c r="H4" t="s">
         <v>20</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="7" t="s">
         <v>15</v>
       </c>
       <c r="K4" t="s">
@@ -660,7 +660,7 @@
       <c r="F5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="7" t="s">
         <v>18</v>
       </c>
       <c r="H5" t="s">
@@ -704,7 +704,7 @@
       <c r="I6" t="s">
         <v>12</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="K6" t="s">
@@ -712,6 +712,181 @@
       </c>
       <c r="L6" s="5">
         <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L7" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L9" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" t="s">
+        <v>16</v>
+      </c>
+      <c r="L10" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" s="5">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/vip2025.xlsx
+++ b/data/vip2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isabelhaas/Documents/Coding/aytogermany/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{03B1CF5B-EF22-AF4A-B113-C0E57384EF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805FC4C3-AFAA-9041-8519-5BC3B6164E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="760" windowWidth="29620" windowHeight="13820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="760" windowWidth="33720" windowHeight="17820" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Candidates" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,11 @@
     <sheet name="Solution" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="28">
   <si>
     <t>left</t>
   </si>
@@ -108,12 +107,6 @@
   </si>
   <si>
     <t>result</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>true</t>
   </si>
 </sst>
 </file>
@@ -1478,7 +1471,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -1508,8 +1501,8 @@
       <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
-        <v>28</v>
+      <c r="D2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1522,8 +1515,8 @@
       <c r="C3" t="s">
         <v>24</v>
       </c>
-      <c r="D3" t="s">
-        <v>29</v>
+      <c r="D3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1536,8 +1529,8 @@
       <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" t="s">
-        <v>28</v>
+      <c r="D4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1550,8 +1543,8 @@
       <c r="C5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" t="s">
-        <v>28</v>
+      <c r="D5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1564,8 +1557,8 @@
       <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" t="s">
-        <v>28</v>
+      <c r="D6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1578,8 +1571,8 @@
       <c r="C7" t="s">
         <v>5</v>
       </c>
-      <c r="D7" t="s">
-        <v>28</v>
+      <c r="D7" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1592,8 +1585,8 @@
       <c r="C8" t="s">
         <v>5</v>
       </c>
-      <c r="D8" t="s">
-        <v>28</v>
+      <c r="D8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1606,8 +1599,8 @@
       <c r="C9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" t="s">
-        <v>29</v>
+      <c r="D9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1620,8 +1613,8 @@
       <c r="C10" t="s">
         <v>5</v>
       </c>
-      <c r="D10" t="s">
-        <v>28</v>
+      <c r="D10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1634,8 +1627,8 @@
       <c r="C11" t="s">
         <v>19</v>
       </c>
-      <c r="D11" t="s">
-        <v>28</v>
+      <c r="D11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1648,8 +1641,8 @@
       <c r="C12" t="s">
         <v>5</v>
       </c>
-      <c r="D12" t="s">
-        <v>28</v>
+      <c r="D12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1662,8 +1655,22 @@
       <c r="C13" t="s">
         <v>23</v>
       </c>
-      <c r="D13" t="s">
-        <v>28</v>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/vip2025.xlsx
+++ b/data/vip2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isabelhaas/Documents/Coding/aytogermany/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805FC4C3-AFAA-9041-8519-5BC3B6164E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE00C2A-79AD-734A-920B-9AB7526FC16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="760" windowWidth="33720" windowHeight="17820" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="560" yWindow="1940" windowWidth="18620" windowHeight="21020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Candidates" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="28">
   <si>
     <t>left</t>
   </si>
@@ -82,9 +82,6 @@
     <t>Nelly</t>
   </si>
   <si>
-    <t>Olli</t>
-  </si>
-  <si>
     <t>Sandra</t>
   </si>
   <si>
@@ -107,6 +104,9 @@
   </si>
   <si>
     <t>result</t>
+  </si>
+  <si>
+    <t>Oliver</t>
   </si>
 </sst>
 </file>
@@ -1031,28 +1031,28 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
         <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
         <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1122,7 +1122,7 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>4</v>
@@ -1131,10 +1131,10 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
@@ -1154,22 +1154,22 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
         <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>4</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
         <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3" t="s">
         <v>11</v>
@@ -1183,7 +1183,7 @@
     </row>
     <row r="4" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
@@ -1192,10 +1192,10 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
@@ -1218,19 +1218,19 @@
     </row>
     <row r="5" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
       </c>
       <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
         <v>15</v>
@@ -1253,19 +1253,19 @@
     </row>
     <row r="6" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
@@ -1297,16 +1297,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H7" t="s">
         <v>4</v>
@@ -1332,19 +1332,19 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I8" t="s">
         <v>15</v>
@@ -1367,19 +1367,19 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G9" t="s">
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
@@ -1399,16 +1399,16 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
         <v>23</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
         <v>7</v>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K10">
         <v>4</v>
@@ -1431,22 +1431,22 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H11" t="s">
         <v>4</v>
@@ -1471,7 +1471,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -1479,7 +1479,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1488,46 +1488,46 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
@@ -1538,10 +1538,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -1549,13 +1549,13 @@
     </row>
     <row r="6" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -1563,27 +1563,27 @@
     </row>
     <row r="7" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
@@ -1591,86 +1591,58 @@
     </row>
     <row r="9" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
         <v>5</v>
       </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
       <c r="D9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
         <v>7</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>5</v>
       </c>
       <c r="D12" t="b">
         <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1731,7 +1703,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1739,7 +1711,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -1747,7 +1719,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -1763,7 +1735,7 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -1776,7 +1748,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
@@ -1784,7 +1756,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>

--- a/data/vip2025.xlsx
+++ b/data/vip2025.xlsx
@@ -1,29 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isabelhaas/Documents/Coding/aytogermany/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE00C2A-79AD-734A-920B-9AB7526FC16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="560" yWindow="1940" windowWidth="18620" windowHeight="21020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Candidates" sheetId="1" r:id="rId1"/>
-    <sheet name="Nights" sheetId="2" r:id="rId2"/>
-    <sheet name="Matchboxes" sheetId="3" r:id="rId3"/>
-    <sheet name="Solution" sheetId="4" r:id="rId4"/>
+    <sheet sheetId="1" name="Candidates" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Nights" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Matchboxes" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Solution" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="33">
   <si>
     <t>left</t>
   </si>
@@ -82,6 +73,9 @@
     <t>Nelly</t>
   </si>
   <si>
+    <t>Oliver</t>
+  </si>
+  <si>
     <t>Sandra</t>
   </si>
   <si>
@@ -103,153 +97,54 @@
     <t>episode</t>
   </si>
   <si>
+    <t>Frau</t>
+  </si>
+  <si>
+    <t>Mann</t>
+  </si>
+  <si>
     <t>result</t>
   </si>
   <si>
-    <t>Oliver</t>
+    <t>before_night</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>false</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Cambria"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <color rgb="FF2C3E50"/>
       <sz val="12"/>
-      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <color rgb="FF2C3E50"/>
       <sz val="12"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -258,185 +153,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFC5C6C7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -444,210 +165,27 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -796,6 +334,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
@@ -806,31 +345,27 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
+              <a:shade val="95000"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -852,7 +387,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -910,7 +445,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
+                <a:shade val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -923,12 +458,13 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
+                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -940,34 +476,71 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="10.714285714285714" customWidth="1"/>
+    <col min="4" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="19.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="17.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -978,7 +551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -986,7 +559,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -994,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1002,7 +575,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1010,7 +583,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1018,7 +591,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1026,92 +599,91 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="17.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" ht="17.25" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" ht="17.25" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="11" width="10.714285714285714" customWidth="1"/>
+    <col min="12" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="17.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1122,7 +694,7 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>4</v>
@@ -1131,10 +703,10 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
@@ -1146,7 +718,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="17.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1154,22 +726,22 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>4</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
         <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
         <v>11</v>
@@ -1181,9 +753,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="17.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
@@ -1192,10 +764,10 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
@@ -1216,21 +788,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="17.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
         <v>15</v>
@@ -1251,21 +823,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="17.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
@@ -1286,7 +858,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="17.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1297,16 +869,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7" t="s">
         <v>4</v>
@@ -1321,7 +893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="17.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1332,19 +904,19 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I8" t="s">
         <v>15</v>
@@ -1356,7 +928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="17.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1367,19 +939,19 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G9" t="s">
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
@@ -1391,7 +963,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="17.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1399,16 +971,16 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G10" t="s">
         <v>7</v>
@@ -1420,33 +992,33 @@
         <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" ht="17.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
       </c>
       <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
         <v>23</v>
-      </c>
-      <c r="E11" t="s">
-        <v>22</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" t="s">
         <v>4</v>
@@ -1463,35 +1035,37 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="10.714285714285714" customWidth="1"/>
+    <col min="5" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
+    <row r="1" ht="17.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1499,13 +1073,16 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" ht="17.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1515,11 +1092,14 @@
       <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1529,25 +1109,31 @@
       <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" ht="17.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1557,25 +1143,31 @@
       <c r="C6" t="s">
         <v>5</v>
       </c>
-      <c r="D6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" ht="17.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1583,13 +1175,16 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" ht="17.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1599,11 +1194,14 @@
       <c r="C9" t="s">
         <v>5</v>
       </c>
-      <c r="D9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" ht="17.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1611,13 +1209,16 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1627,11 +1228,14 @@
       <c r="C11" t="s">
         <v>4</v>
       </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -1641,32 +1245,37 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" t="b">
-        <v>0</v>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1674,7 +1283,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1682,7 +1291,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1690,7 +1299,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1698,31 +1307,31 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1730,15 +1339,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1746,23 +1355,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>